--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N20_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,23 +480,55 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>14.10862641948917</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.204715043450688</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.727223659328008</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5915156154063155</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N20.png</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
         <v>8.654179100833154</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>5.021683812638057</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2.727223659328008</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5915156154063155</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.10862641948917</v>
+        <v>2.29265179316699</v>
       </c>
       <c r="D2" t="n">
-        <v>6.204715043450688</v>
+        <v>1.008266194560737</v>
       </c>
       <c r="E2" t="n">
-        <v>2.727223659328008</v>
+        <v>0.4431738446408012</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5915156154063155</v>
+        <v>0.09612128750352622</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.654179100833154</v>
+        <v>1.406304103885388</v>
       </c>
       <c r="D3" t="n">
-        <v>5.021683812638057</v>
+        <v>0.8160236195536843</v>
       </c>
       <c r="E3" t="n">
-        <v>2.727223659328008</v>
+        <v>0.4431738446408012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5915156154063155</v>
+        <v>0.09612128750352622</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
